--- a/artfynd/A 7965-2024 artfynd.xlsx
+++ b/artfynd/A 7965-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120360416</v>
+        <v>120359137</v>
       </c>
       <c r="B2" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513062</v>
+        <v>513089</v>
       </c>
       <c r="R2" t="n">
-        <v>6761693</v>
+        <v>6761716</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120357425</v>
+        <v>120358859</v>
       </c>
       <c r="B3" t="n">
         <v>90864</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120359137</v>
+        <v>120360416</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,31 +1054,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513089</v>
+        <v>513062</v>
       </c>
       <c r="R5" t="n">
-        <v>6761716</v>
+        <v>6761693</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 7965-2024 artfynd.xlsx
+++ b/artfynd/A 7965-2024 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120360369</v>
+        <v>120360416</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,43 +933,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513097</v>
+        <v>513062</v>
       </c>
       <c r="R4" t="n">
-        <v>6761781</v>
+        <v>6761693</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120360416</v>
+        <v>120360369</v>
       </c>
       <c r="B5" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,43 +1054,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513062</v>
+        <v>513097</v>
       </c>
       <c r="R5" t="n">
-        <v>6761693</v>
+        <v>6761781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 7965-2024 artfynd.xlsx
+++ b/artfynd/A 7965-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120359137</v>
+        <v>120360369</v>
       </c>
       <c r="B2" t="n">
         <v>90580</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513089</v>
+        <v>513097</v>
       </c>
       <c r="R2" t="n">
-        <v>6761716</v>
+        <v>6761781</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120358859</v>
+        <v>120357425</v>
       </c>
       <c r="B3" t="n">
         <v>90864</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120360369</v>
+        <v>120359137</v>
       </c>
       <c r="B5" t="n">
         <v>90580</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513097</v>
+        <v>513089</v>
       </c>
       <c r="R5" t="n">
-        <v>6761781</v>
+        <v>6761716</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 7965-2024 artfynd.xlsx
+++ b/artfynd/A 7965-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120360369</v>
+        <v>120359137</v>
       </c>
       <c r="B2" t="n">
         <v>90580</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513097</v>
+        <v>513089</v>
       </c>
       <c r="R2" t="n">
-        <v>6761781</v>
+        <v>6761716</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120357425</v>
+        <v>120360416</v>
       </c>
       <c r="B3" t="n">
         <v>90864</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -841,14 +841,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513097</v>
+        <v>513062</v>
       </c>
       <c r="R3" t="n">
-        <v>6761781</v>
+        <v>6761693</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120360416</v>
+        <v>120357425</v>
       </c>
       <c r="B4" t="n">
         <v>90864</v>
@@ -952,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -962,14 +962,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513062</v>
+        <v>513097</v>
       </c>
       <c r="R4" t="n">
-        <v>6761693</v>
+        <v>6761781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120359137</v>
+        <v>120360369</v>
       </c>
       <c r="B5" t="n">
         <v>90580</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513089</v>
+        <v>513097</v>
       </c>
       <c r="R5" t="n">
-        <v>6761716</v>
+        <v>6761781</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 7965-2024 artfynd.xlsx
+++ b/artfynd/A 7965-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120359137</v>
+        <v>120358859</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513089</v>
+        <v>513097</v>
       </c>
       <c r="R2" t="n">
-        <v>6761716</v>
+        <v>6761781</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120357425</v>
+        <v>120360369</v>
       </c>
       <c r="B4" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,31 +933,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120360369</v>
+        <v>120359137</v>
       </c>
       <c r="B5" t="n">
         <v>90580</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513097</v>
+        <v>513089</v>
       </c>
       <c r="R5" t="n">
-        <v>6761781</v>
+        <v>6761716</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,6 +1156,248 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120538656</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>513065</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6761744</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120537885</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90545</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>513113</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6761801</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7965-2024 artfynd.xlsx
+++ b/artfynd/A 7965-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120358859</v>
+        <v>120360416</v>
       </c>
       <c r="B2" t="n">
         <v>90864</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513097</v>
+        <v>513062</v>
       </c>
       <c r="R2" t="n">
-        <v>6761781</v>
+        <v>6761693</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120360416</v>
+        <v>120358728</v>
       </c>
       <c r="B3" t="n">
         <v>90864</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -841,14 +841,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513062</v>
+        <v>513097</v>
       </c>
       <c r="R3" t="n">
-        <v>6761693</v>
+        <v>6761781</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120360369</v>
+        <v>120359137</v>
       </c>
       <c r="B4" t="n">
         <v>90580</v>
@@ -952,7 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -962,17 +962,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513097</v>
+        <v>513089</v>
       </c>
       <c r="R4" t="n">
-        <v>6761781</v>
+        <v>6761716</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120359137</v>
+        <v>120360369</v>
       </c>
       <c r="B5" t="n">
         <v>90580</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513089</v>
+        <v>513097</v>
       </c>
       <c r="R5" t="n">
-        <v>6761716</v>
+        <v>6761781</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 7965-2024 artfynd.xlsx
+++ b/artfynd/A 7965-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1880,6 +1880,127 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120679427</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91137</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>513069</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6761693</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7965-2024 artfynd.xlsx
+++ b/artfynd/A 7965-2024 artfynd.xlsx
@@ -1885,7 +1885,7 @@
         <v>120679427</v>
       </c>
       <c r="B12" t="n">
-        <v>91137</v>
+        <v>91149</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 7965-2024 artfynd.xlsx
+++ b/artfynd/A 7965-2024 artfynd.xlsx
@@ -1885,7 +1885,7 @@
         <v>120679427</v>
       </c>
       <c r="B12" t="n">
-        <v>91149</v>
+        <v>91150</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 7965-2024 artfynd.xlsx
+++ b/artfynd/A 7965-2024 artfynd.xlsx
@@ -1885,7 +1885,7 @@
         <v>120679427</v>
       </c>
       <c r="B12" t="n">
-        <v>91150</v>
+        <v>91153</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 7965-2024 artfynd.xlsx
+++ b/artfynd/A 7965-2024 artfynd.xlsx
@@ -1885,7 +1885,7 @@
         <v>120679427</v>
       </c>
       <c r="B12" t="n">
-        <v>91153</v>
+        <v>91159</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 7965-2024 artfynd.xlsx
+++ b/artfynd/A 7965-2024 artfynd.xlsx
@@ -1885,7 +1885,7 @@
         <v>120679427</v>
       </c>
       <c r="B12" t="n">
-        <v>91159</v>
+        <v>91160</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 7965-2024 artfynd.xlsx
+++ b/artfynd/A 7965-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>120357425</v>
       </c>
       <c r="B2" t="n">
-        <v>90926</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -796,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120360369</v>
+        <v>120358200</v>
       </c>
       <c r="B3" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,19 +826,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513097</v>
+        <v>513144</v>
       </c>
       <c r="R3" t="n">
-        <v>6761781</v>
+        <v>6761792</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120359137</v>
+        <v>120360127</v>
       </c>
       <c r="B4" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,31 +918,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -966,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513089</v>
+        <v>513050</v>
       </c>
       <c r="R4" t="n">
-        <v>6761716</v>
+        <v>6761639</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,12 +1026,7 @@
         <v>120360416</v>
       </c>
       <c r="B5" t="n">
-        <v>90926</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,12 +1043,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1159,62 +1139,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120537885</v>
+        <v>120683593</v>
       </c>
       <c r="B6" t="n">
-        <v>90644</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lenåsmyren, Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513113</v>
+        <v>513069</v>
       </c>
       <c r="R6" t="n">
-        <v>6761801</v>
+        <v>6761776</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,22 +1215,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,6 +1239,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1273,22 +1251,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Irina Röjås</t>
+          <t>Irina Röjås, Anna-Britt Olsson, Rolf Blomqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120538656</v>
+        <v>120357569</v>
       </c>
       <c r="B7" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,21 +1269,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1320,7 +1293,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1329,13 +1302,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513065</v>
+        <v>513095</v>
       </c>
       <c r="R7" t="n">
-        <v>6761744</v>
+        <v>6761826</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1359,22 +1332,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,47 +1374,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120683495</v>
+        <v>120359137</v>
       </c>
       <c r="B8" t="n">
-        <v>91119</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1450,13 +1418,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513069</v>
+        <v>513089</v>
       </c>
       <c r="R8" t="n">
-        <v>6761776</v>
+        <v>6761716</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1480,22 +1448,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,53 +1490,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120678546</v>
+        <v>120360369</v>
       </c>
       <c r="B9" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+          <t>Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513078</v>
+        <v>513097</v>
       </c>
       <c r="R9" t="n">
-        <v>6761719</v>
+        <v>6761781</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1592,22 +1564,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1634,15 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120683593</v>
+        <v>120677966</v>
       </c>
       <c r="B10" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,48 +1617,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lenåsmyren, Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513069</v>
+        <v>513107</v>
       </c>
       <c r="R10" t="n">
-        <v>6761776</v>
+        <v>6761832</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1720,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1730,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,7 +1704,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1751,22 +1715,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Irina Röjås, Anna-Britt Olsson, Rolf Blomqvist</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120678666</v>
+        <v>120679427</v>
       </c>
       <c r="B11" t="n">
-        <v>90117</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,48 +1733,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2008</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lenåsmyren, Lenåsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513097</v>
+        <v>513069</v>
       </c>
       <c r="R11" t="n">
-        <v>6761746</v>
+        <v>6761693</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1844,7 +1801,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1811,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,7 +1820,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1875,26 +1831,21 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Irina Röjås, Anna-Britt Olsson, Rolf Blomqvist</t>
+          <t>Irina Röjås</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120679427</v>
+        <v>120683495</v>
       </c>
       <c r="B12" t="n">
-        <v>91168</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1907,12 +1858,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1934,10 +1885,10 @@
         <v>513069</v>
       </c>
       <c r="R12" t="n">
-        <v>6761693</v>
+        <v>6761776</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1966,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1976,7 +1927,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2000,6 +1951,904 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120678666</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91333</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Geastrum quadrifidum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>513097</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6761746</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Irina Röjås, Anna-Britt Olsson, Rolf Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120357077</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lenåsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>513095</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6761826</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120359835</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>513068</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6761637</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120360281</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>513050</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6761639</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120357689</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>513095</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6761826</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120537885</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>513113</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6761801</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120538656</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>513065</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6761744</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120678546</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lenåsmyren, Lenåsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>513078</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6761719</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Irina Röjås</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7965-2024 artfynd.xlsx
+++ b/artfynd/A 7965-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120357425</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120358200</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120360127</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120360416</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1255,6 +1280,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683593</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1371,6 +1401,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120357569</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1487,6 +1522,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120359137</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1603,6 +1643,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120360369</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1719,6 +1764,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120677966</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1835,6 +1885,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120679427</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1951,6 +2006,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683495</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2070,6 +2130,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120678666</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2176,6 +2241,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120357077</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2292,6 +2362,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120359835</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2403,6 +2478,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120360281</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2510,6 +2590,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120357689</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2626,6 +2711,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120537885</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2742,6 +2832,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120538656</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2849,8 +2944,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120678546</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>